--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Type de structure</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>Catégorie d'établissement provenant du jdv FHIR https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j368-categorie-etablissement-cisis</t>
@@ -1041,13 +1044,13 @@
         <v>73</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>73</v>
@@ -1082,10 +1085,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1108,13 +1111,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1165,7 +1168,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
@@ -1182,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1208,13 +1211,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1265,7 +1268,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -1282,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1308,13 +1311,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1365,7 +1368,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
@@ -1382,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1408,13 +1411,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1465,7 +1468,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -1482,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1511,10 +1514,10 @@
         <v>83</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1541,13 +1544,13 @@
         <v>73</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>73</v>
@@ -1565,7 +1568,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
